--- a/Asignaciones/Tablero/temp_html2.xlsx
+++ b/Asignaciones/Tablero/temp_html2.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="plantilla" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Participantes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plantilla" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participantes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_Hlk52262180" localSheetId="0">plantilla!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'plantilla'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'plantilla'!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -227,9 +227,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="20" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -271,16 +268,22 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -289,6 +292,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -299,14 +308,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -317,8 +323,8 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -327,12 +333,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -738,55 +738,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col width="5.33203125" customWidth="1" style="27" min="1" max="1"/>
-    <col width="1.21875" customWidth="1" style="27" min="2" max="2"/>
-    <col width="2.44140625" customWidth="1" style="27" min="3" max="3"/>
-    <col width="28.88671875" customWidth="1" style="27" min="5" max="5"/>
-    <col width="13.6640625" customWidth="1" style="27" min="6" max="6"/>
-    <col width="18.44140625" customWidth="1" style="27" min="7" max="8"/>
-    <col width="18.44140625" customWidth="1" style="15" min="9" max="10"/>
-    <col width="10.77734375" customWidth="1" style="15" min="11" max="13"/>
-    <col width="3.21875" customWidth="1" style="15" min="14" max="15"/>
-    <col width="4.44140625" customWidth="1" style="15" min="16" max="16"/>
-    <col width="16.21875" customWidth="1" style="27" min="17" max="17"/>
-    <col width="19.109375" customWidth="1" style="27" min="18" max="18"/>
+    <col width="5.33203125" customWidth="1" style="28" min="1" max="1"/>
+    <col width="1.21875" customWidth="1" style="28" min="2" max="2"/>
+    <col width="2.44140625" customWidth="1" style="28" min="3" max="3"/>
+    <col width="28.88671875" customWidth="1" style="28" min="5" max="5"/>
+    <col width="13.6640625" customWidth="1" style="28" min="6" max="6"/>
+    <col width="18.44140625" customWidth="1" style="28" min="7" max="8"/>
+    <col width="18.44140625" customWidth="1" style="14" min="9" max="10"/>
+    <col width="10.77734375" customWidth="1" style="14" min="11" max="13"/>
+    <col width="3.21875" customWidth="1" style="14" min="14" max="15"/>
+    <col width="4.44140625" customWidth="1" style="14" min="16" max="16"/>
+    <col width="16.21875" customWidth="1" style="28" min="17" max="17"/>
+    <col width="19.109375" customWidth="1" style="28" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.6" customHeight="1" s="27" thickBot="1">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="21.6" customHeight="1" s="28" thickBot="1">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>La Gatazo</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="31" t="inlineStr">
         <is>
           <t>Programa para la reunión de entre semana</t>
         </is>
       </c>
-      <c r="E1" s="29" t="n"/>
-      <c r="F1" s="29" t="n"/>
-      <c r="G1" s="29" t="n"/>
-      <c r="H1" s="29" t="n"/>
-    </row>
-    <row r="2" ht="12.6" customHeight="1" s="27" thickTop="1">
+      <c r="E1" s="32" t="n"/>
+      <c r="F1" s="32" t="n"/>
+      <c r="G1" s="32" t="n"/>
+      <c r="H1" s="32" t="n"/>
+    </row>
+    <row r="2" ht="12.6" customHeight="1" s="28" thickTop="1">
       <c r="A2" s="45">
         <f>+I2</f>
         <v/>
       </c>
-      <c r="B2" s="41" t="n"/>
-      <c r="C2" s="41" t="n"/>
+      <c r="B2" s="43" t="n"/>
+      <c r="C2" s="43" t="n"/>
       <c r="D2" s="46" t="n"/>
-      <c r="E2" s="40">
+      <c r="E2" s="42">
         <f>+J2</f>
         <v/>
       </c>
-      <c r="F2" s="41" t="n"/>
-      <c r="G2" s="33" t="inlineStr">
+      <c r="F2" s="43" t="n"/>
+      <c r="G2" s="35" t="inlineStr">
         <is>
           <t>Presidente</t>
         </is>
@@ -795,27 +795,30 @@
         <f>+K2</f>
         <v/>
       </c>
-      <c r="I2" s="36" t="inlineStr">
-        <is>
-          <t>16-22 DE MARZO</t>
-        </is>
-      </c>
-      <c r="J2" s="36" t="inlineStr">
-        <is>
-          <t>ISAÍAS 45-47</t>
+      <c r="I2" s="38" t="inlineStr">
+        <is>
+          <t>12-18 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="J2" s="38" t="inlineStr">
+        <is>
+          <t>JEREMÍAS 42-44</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Israel Rocha</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="12.6" customHeight="1" s="27">
+          <t>Marcos España</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="3" ht="12.6" customHeight="1" s="28">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
-      <c r="F3" s="33" t="inlineStr">
+      <c r="F3" s="35" t="inlineStr">
         <is>
           <t>Consejero de la Sala Auxiliar</t>
         </is>
@@ -824,28 +827,28 @@
         <f>+K3</f>
         <v/>
       </c>
-      <c r="I3" s="36" t="n"/>
-      <c r="J3" s="36" t="n"/>
+      <c r="I3" s="38" t="n"/>
+      <c r="J3" s="38" t="n"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Luis Chamorro</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="12.6" customHeight="1" s="27">
-      <c r="A4" s="35" t="n">
+          <t>Freddy Velazco</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="12.6" customHeight="1" s="28">
+      <c r="A4" s="37" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="B4" s="35" t="n"/>
-      <c r="C4" s="6">
+      <c r="B4" s="37" t="n"/>
+      <c r="C4" s="5">
         <f>+"■"</f>
         <v/>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="38">
         <f>+I4</f>
         <v/>
       </c>
-      <c r="G4" s="33" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>Oración</t>
         </is>
@@ -854,65 +857,64 @@
         <f>+K4</f>
         <v/>
       </c>
-      <c r="I4" s="36" t="inlineStr">
-        <is>
-          <t>Canción 2: Tu nombre es Jehová</t>
-        </is>
-      </c>
-      <c r="J4" s="36" t="n"/>
+      <c r="I4" s="38" t="inlineStr">
+        <is>
+          <t>Canción 103: Nuestros pastores son un regalo de Dios</t>
+        </is>
+      </c>
+      <c r="J4" s="38" t="n"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Manuel Vizcaino</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="12.6" customHeight="1" s="27">
-      <c r="A5" s="35" t="n">
+          <t>Jaime Mera</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="12.6" customHeight="1" s="28">
+      <c r="A5" s="37" t="n">
         <v>0.7951388888888888</v>
       </c>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="6">
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="5">
         <f>+"■"</f>
         <v/>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Palabras de Introducción (1 min.)</t>
         </is>
       </c>
       <c r="H5" s="2" t="n"/>
-      <c r="I5" s="36" t="n"/>
-      <c r="J5" s="22" t="n"/>
-      <c r="Q5" s="19" t="n"/>
-    </row>
-    <row r="6" ht="12.6" customHeight="1" s="27">
+      <c r="I5" s="38" t="n"/>
+      <c r="Q5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="12.6" customHeight="1" s="28">
       <c r="A6" s="44" t="inlineStr">
         <is>
           <t>Tesoros de la Biblia</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Sala Auxiliar</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Auditorio Principal</t>
         </is>
       </c>
-      <c r="I6" s="23" t="n"/>
-      <c r="J6" s="23" t="n"/>
-    </row>
-    <row r="7" ht="16.8" customHeight="1" s="27">
-      <c r="A7" s="35" t="n">
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="22" t="n"/>
+    </row>
+    <row r="7" ht="16.8" customHeight="1" s="28">
+      <c r="A7" s="37" t="n">
         <v>0.7958333333333333</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="30">
         <f>+"1."</f>
         <v/>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="24">
         <f>RIGHT(I7,LEN(I7)-SEARCH(". ",I7)-1)&amp;" ("&amp;J7&amp;")"</f>
         <v/>
       </c>
@@ -920,31 +922,31 @@
         <f>+K7</f>
         <v/>
       </c>
-      <c r="I7" s="36" t="inlineStr">
-        <is>
-          <t>1. “Yo soy Dios, y no hay nadie como yo”</t>
-        </is>
-      </c>
-      <c r="J7" s="36" t="inlineStr">
+      <c r="I7" s="38" t="inlineStr">
+        <is>
+          <t>1. Pidieron guía y luego la rechazaron</t>
+        </is>
+      </c>
+      <c r="J7" s="38" t="inlineStr">
         <is>
           <t>10 mins.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Antonio Zambrano</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.8" customHeight="1" s="27">
-      <c r="A8" s="35" t="n">
+          <t>Manuel Vizcaino</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.8" customHeight="1" s="28">
+      <c r="A8" s="37" t="n">
         <v>0.8027777777777778</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="30">
         <f>+"2."</f>
         <v/>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>Busquemos perlas escondidas (10 mins.)</t>
         </is>
@@ -953,28 +955,28 @@
         <f>+K8</f>
         <v/>
       </c>
-      <c r="I8" s="36" t="n"/>
-      <c r="J8" s="36" t="n"/>
+      <c r="I8" s="38" t="n"/>
+      <c r="J8" s="38" t="n"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Marcelo Moreano</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16.8" customHeight="1" s="27">
-      <c r="A9" s="35" t="n">
+          <t>Jamin Merchan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16.8" customHeight="1" s="28">
+      <c r="A9" s="37" t="n">
         <v>0.8097222222222222</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="30">
         <f>+"3."</f>
         <v/>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Lectura de la Biblia (4 mins.)</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
+      <c r="F9" s="35" t="inlineStr">
         <is>
           <t>Estudiante:</t>
         </is>
@@ -987,82 +989,72 @@
         <f>+K9</f>
         <v/>
       </c>
-      <c r="I9" s="36" t="n"/>
-      <c r="J9" s="36" t="n"/>
+      <c r="I9" s="38" t="n"/>
+      <c r="J9" s="38" t="n"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Michael Cadena</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>3. Lectura de la Biblia</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>4 mins.</t>
+          <t>Jonathan Nieto</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Mateo Peralta</t>
+          <t>Sebastian Carrera</t>
         </is>
       </c>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
     </row>
-    <row r="10" ht="12.6" customHeight="1" s="27">
-      <c r="A10" s="39" t="inlineStr">
+    <row r="10" ht="12.6" customHeight="1" s="28">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>Seamos Mejores Maestros</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>Sala Auxiliar</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Auditorio Principal</t>
         </is>
       </c>
-      <c r="I10" s="23" t="n"/>
-      <c r="J10" s="23" t="n"/>
-      <c r="Q10" s="17" t="n"/>
-    </row>
-    <row r="11" ht="13.8" customHeight="1" s="27">
-      <c r="A11" s="35">
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="Q10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="13.8" customHeight="1" s="28">
+      <c r="A11" s="37">
         <f>A9+TEXT(LEFT(M11, FIND(" ", M11)-1)/1440, "hh:mm")</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="30">
         <f>+"4."</f>
         <v/>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="34">
         <f>RIGHT(L11,LEN(L11)-SEARCH(". ",L11)-1)&amp;" ("&amp;M11&amp;")"</f>
         <v/>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>Estudiante/Ayudante:</t>
         </is>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="33">
         <f>Q11&amp;" / "&amp;Q12</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="33">
         <f>K11&amp;" / "&amp;K12</f>
         <v/>
       </c>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="36" t="n"/>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="38" t="n"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Scarlett Luna</t>
+          <t>Alex Calvache</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1070,66 +1062,65 @@
           <t>4. Empiece conversaciones</t>
         </is>
       </c>
-      <c r="M11" s="25" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t>3 mins.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Angélica Rocha</t>
+          <t>Daniel Valencia</t>
         </is>
       </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
     </row>
-    <row r="12" ht="13.8" customHeight="1" s="27">
-      <c r="J12" s="25" t="n"/>
+    <row r="12" ht="13.8" customHeight="1" s="28">
+      <c r="J12" s="26" t="n"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Carmelina Tualombo</t>
-        </is>
-      </c>
-      <c r="M12" s="25" t="n"/>
+          <t>Fernando Cajas</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Ana de Lugmaña</t>
+          <t>Pedro Apolinario</t>
         </is>
       </c>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
     </row>
-    <row r="13" ht="13.8" customHeight="1" s="27">
-      <c r="A13" s="35">
+    <row r="13" ht="13.8" customHeight="1" s="28">
+      <c r="A13" s="37">
         <f>A11+TEXT(LEFT(M13, FIND(" ", M13)-1)/1440, "hh:mm")</f>
         <v/>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="30">
         <f>+"5."</f>
         <v/>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="34">
         <f>RIGHT(L13,LEN(L13)-SEARCH(". ",L13)-1)&amp;" ("&amp;M13&amp;")"</f>
         <v/>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>Estudiante/Ayudante:</t>
         </is>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="33">
         <f>Q13&amp;" / "&amp;Q14</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="33">
         <f>K13&amp;" / "&amp;K14</f>
         <v/>
       </c>
-      <c r="I13" s="24" t="n"/>
-      <c r="J13" s="36" t="n"/>
+      <c r="I13" s="23" t="n"/>
+      <c r="J13" s="38" t="n"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Edixon Colina</t>
+          <t>Marlene de Rocha</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1137,140 +1128,119 @@
           <t>5. Haga revisitas</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>4 mins.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Gabriela de Quiñonez</t>
+          <t>Keily Moreano</t>
         </is>
       </c>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
     </row>
-    <row r="14" ht="13.8" customHeight="1" s="27">
+    <row r="14" ht="13.8" customHeight="1" s="28">
       <c r="K14" t="inlineStr">
         <is>
-          <t>Luis Jiménez</t>
-        </is>
-      </c>
-      <c r="M14" s="25" t="n"/>
+          <t>Teresa Jativa</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Jeaneth Castro</t>
+          <t>Teresa de Alarcón</t>
         </is>
       </c>
       <c r="R14" s="2" t="n"/>
       <c r="S14" s="2" t="n"/>
     </row>
-    <row r="15" ht="13.8" customHeight="1" s="27">
-      <c r="A15" s="35">
+    <row r="15" ht="13.8" customHeight="1" s="28">
+      <c r="A15" s="37">
         <f>A13+TEXT(LEFT(M15, FIND(" ", M15)-1)/1440, "hh:mm")</f>
         <v/>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="30">
         <f>+"6."</f>
         <v/>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="34">
         <f>RIGHT(L15,LEN(L15)-SEARCH(". ",L15)-1)&amp;" ("&amp;M15&amp;")"</f>
         <v/>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>Estudiante/Ayudante:</t>
         </is>
       </c>
-      <c r="G15" s="30">
-        <f>IFERROR(Q15 &amp; " / " &amp; Q16,Q15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="30">
-        <f>IFERROR(K15 &amp; " / " &amp; K16,K15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="24" t="n"/>
-      <c r="J15" s="36" t="n"/>
+      <c r="G15" s="33">
+        <f>Q15&amp;" / "&amp;Q16</f>
+        <v/>
+      </c>
+      <c r="H15" s="33">
+        <f>K15&amp;" / "&amp;K16</f>
+        <v/>
+      </c>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="38" t="n"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Byron Vela</t>
+          <t>Edwin Encalada</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6. Haga discípulos</t>
-        </is>
-      </c>
-      <c r="M15" s="25" t="inlineStr">
-        <is>
-          <t>5 mins.</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Kesia de Muñoz</t>
+          <t>6. ¿Qué diría?</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6 mins.</t>
         </is>
       </c>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
     </row>
-    <row r="16" ht="13.8" customHeight="1" s="27">
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Wilson Alarcón</t>
-        </is>
-      </c>
-      <c r="M16" s="25" t="n"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Valeria de Chicaiza</t>
-        </is>
-      </c>
+    <row r="16" ht="13.8" customHeight="1" s="28">
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
     </row>
-    <row r="17" ht="12.6" customHeight="1" s="27">
-      <c r="A17" s="37" t="inlineStr">
+    <row r="17" ht="12.6" customHeight="1" s="28">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Nuestra Vida Cristiana</t>
         </is>
       </c>
-      <c r="M17" s="25" t="n"/>
-    </row>
-    <row r="18" ht="12.6" customHeight="1" s="27">
-      <c r="A18" s="35" t="n">
-        <v>0.8229166666666666</v>
-      </c>
-      <c r="C18" s="12">
+    </row>
+    <row r="18" ht="12.6" customHeight="1" s="28">
+      <c r="A18" s="37" t="n">
+        <v>0.8236111111111111</v>
+      </c>
+      <c r="C18" s="11">
         <f>+"■"</f>
         <v/>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="38">
         <f>+I18</f>
         <v/>
       </c>
-      <c r="H18" s="34" t="n"/>
+      <c r="H18" s="29" t="n"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Canción 38: Jehová te cuidará</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="n"/>
-      <c r="M18" s="25" t="n"/>
-    </row>
-    <row r="19" ht="16.8" customHeight="1" s="27">
-      <c r="A19" s="35">
-        <f>A18+TEXT(LEFT(J19, FIND(" ", J19)-1)/1440, "hh:mm")</f>
-        <v/>
-      </c>
-      <c r="C19" s="32" t="inlineStr">
+          <t>Canción 47: Oremos a Dios todos los días</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16.8" customHeight="1" s="28">
+      <c r="A19" s="37" t="n">
+        <v>0.8277777777777777</v>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>7.</t>
         </is>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="34">
         <f>RIGHT(I19,LEN(I19)-SEARCH(". ",I19)-1)&amp;" ("&amp;J19&amp;")"</f>
         <v/>
       </c>
@@ -1278,230 +1248,216 @@
         <f>+K19</f>
         <v/>
       </c>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="36" t="n"/>
-      <c r="M19" s="25" t="n"/>
-      <c r="Q19" s="14" t="n"/>
-      <c r="R19" s="20" t="n"/>
-    </row>
-    <row r="20" ht="16.8" customHeight="1" s="27">
-      <c r="A20" s="35">
-        <f>A19+TEXT(LEFT(J20, FIND(" ", J20)-1)/1440, "hh:mm")</f>
-        <v/>
-      </c>
-      <c r="C20" s="32" t="inlineStr">
+      <c r="I19" s="38" t="inlineStr">
+        <is>
+          <t>7. Necesidades de la congregación</t>
+        </is>
+      </c>
+      <c r="J19" s="38" t="inlineStr">
+        <is>
+          <t>15 mins.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Rolando Moreano</t>
+        </is>
+      </c>
+      <c r="Q19" s="13" t="n"/>
+      <c r="R19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="28">
+      <c r="A20" s="37" t="n">
+        <v>0.8368055555555556</v>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>8.</t>
         </is>
       </c>
-      <c r="D20" s="31">
-        <f>RIGHT(I20,LEN(I20)-SEARCH(". ",I20)-1)&amp;" ("&amp;J20&amp;")"</f>
-        <v/>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>Estudio bíblico de la congregación (30 mins.)</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>Conductor/Lector:</t>
+        </is>
       </c>
       <c r="H20" s="2">
         <f>+K20</f>
         <v/>
       </c>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-      <c r="M20" s="25" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-      <c r="R20" s="20" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="27">
-      <c r="A21" s="35" t="n">
-        <v>0.8368055555555556</v>
-      </c>
-      <c r="C21" s="32" t="inlineStr">
-        <is>
-          <t>9.</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>Estudio bíblico de la congregación (30 mins.)</t>
-        </is>
-      </c>
-      <c r="G21" s="42" t="inlineStr">
-        <is>
-          <t>Conductor/Lector:</t>
-        </is>
-      </c>
+      <c r="I20" s="38" t="n"/>
+      <c r="J20" s="38" t="n"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Jeremy Ortega</t>
+        </is>
+      </c>
+      <c r="Q20" s="19" t="n"/>
+      <c r="R20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="12.6" customHeight="1" s="28">
       <c r="H21" s="2">
         <f>+K21</f>
         <v/>
       </c>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="36" t="n"/>
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="38" t="n"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Rolando Moreano</t>
-        </is>
-      </c>
-      <c r="Q21" s="20" t="n"/>
-      <c r="R21" s="20" t="n"/>
-    </row>
-    <row r="22" ht="12.6" customHeight="1" s="27">
-      <c r="H22" s="2">
-        <f>+K22</f>
-        <v/>
-      </c>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="n"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Discurso.</t>
-        </is>
-      </c>
-      <c r="Q22" s="19" t="n"/>
-    </row>
-    <row r="23" ht="12.6" customHeight="1" s="27">
-      <c r="A23" s="35" t="n">
+          <t>Adrián Tipantuña</t>
+        </is>
+      </c>
+      <c r="Q21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="12.6" customHeight="1" s="28">
+      <c r="A22" s="37" t="n">
         <v>0.8576388888888888</v>
       </c>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="12">
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="11">
         <f>+"■"</f>
         <v/>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Palabras de conclusión</t>
         </is>
       </c>
-      <c r="E23" s="9" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="36" t="n"/>
-      <c r="J23" s="36" t="n"/>
-      <c r="Q23" s="17" t="n"/>
-    </row>
-    <row r="24" ht="12.6" customHeight="1" s="27">
-      <c r="A24" s="35" t="n">
+      <c r="E22" s="8" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="38" t="n"/>
+      <c r="J22" s="38" t="n"/>
+      <c r="Q22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="12.6" customHeight="1" s="28">
+      <c r="A23" s="37" t="n">
         <v>0.8597222222222223</v>
       </c>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="12">
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="11">
         <f>+"■"</f>
         <v/>
       </c>
-      <c r="D24" s="38">
-        <f>+I24</f>
-        <v/>
-      </c>
-      <c r="G24" s="33" t="inlineStr">
+      <c r="D23" s="36">
+        <f>+I23</f>
+        <v/>
+      </c>
+      <c r="E23" s="8" t="n"/>
+      <c r="G23" s="35" t="inlineStr">
         <is>
           <t>Oración:</t>
         </is>
       </c>
-      <c r="H24" s="2">
-        <f>+K24</f>
-        <v/>
-      </c>
-      <c r="I24" s="36" t="inlineStr">
-        <is>
-          <t>Canción 148: Jehová es mi Roca de salvación</t>
-        </is>
-      </c>
-      <c r="J24" s="36" t="n"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Wilson Rodriguez</t>
-        </is>
-      </c>
-      <c r="Q24" s="14" t="n"/>
-    </row>
-    <row r="25" ht="19.2" customHeight="1" s="27"/>
-    <row r="26" ht="15" customHeight="1" s="27">
-      <c r="A26" s="35" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="F26" s="34" t="n"/>
-      <c r="G26" s="42" t="n"/>
+      <c r="H23" s="2">
+        <f>+K23</f>
+        <v/>
+      </c>
+      <c r="I23" s="38" t="inlineStr">
+        <is>
+          <t>Canción 129: Servimos con aguante</t>
+        </is>
+      </c>
+      <c r="J23" s="38" t="n"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Bolivar Taipe</t>
+        </is>
+      </c>
+      <c r="Q23" s="13" t="n"/>
+    </row>
+    <row r="24" ht="19.2" customHeight="1" s="28"/>
+    <row r="25" ht="15" customHeight="1" s="28">
+      <c r="A25" s="37" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="34" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="38" t="n"/>
+      <c r="J25" s="38" t="n"/>
+      <c r="Q25" s="16" t="n"/>
+      <c r="R25" s="19" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="28">
       <c r="H26" s="2" t="n"/>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="36" t="n"/>
-      <c r="Q26" s="17" t="n"/>
-      <c r="R26" s="20" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="27">
+      <c r="I26" s="38" t="n"/>
+      <c r="J26" s="38" t="n"/>
+      <c r="R26" s="19" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="37" t="n"/>
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
       <c r="H27" s="2" t="n"/>
-      <c r="I27" s="36" t="n"/>
-      <c r="J27" s="36" t="n"/>
-      <c r="R27" s="20" t="n"/>
+      <c r="I27" s="38" t="n"/>
+      <c r="J27" s="38" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="n"/>
-      <c r="B28" s="35" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
+      <c r="A28" s="37" t="n"/>
+      <c r="B28" s="37" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="G28" s="35" t="n"/>
       <c r="H28" s="2" t="n"/>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="36" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="35" t="n"/>
-      <c r="B29" s="35" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="38" t="n"/>
-      <c r="G29" s="33" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="36" t="n"/>
-      <c r="J29" s="36" t="n"/>
-      <c r="Q29" s="16" t="n"/>
-    </row>
-    <row r="30" ht="12" customHeight="1" s="27"/>
+      <c r="I28" s="38" t="n"/>
+      <c r="J28" s="38" t="n"/>
+      <c r="Q28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="12" customHeight="1" s="28"/>
+    <row r="30">
+      <c r="A30" s="3" t="n"/>
+    </row>
     <row r="31">
-      <c r="A31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="U32" s="18" t="n"/>
-    </row>
-    <row r="36">
-      <c r="E36" s="18" t="n"/>
+      <c r="U31" s="17" t="n"/>
+    </row>
+    <row r="35">
+      <c r="E35" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="41">
     <mergeCell ref="F15:F16"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="C20:C21"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="G13:G14"/>
     <mergeCell ref="D15:E16"/>
     <mergeCell ref="H11:H12"/>
-    <mergeCell ref="C26:C27"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="D25:E26"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:C26"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D20:E21"/>
     <mergeCell ref="A17:F17"/>
-    <mergeCell ref="G15:G16"/>
     <mergeCell ref="D19:G19"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D26:E27"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="G20:G21"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="D29:F29"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A13:A14"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A20:A21"/>
     <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G25:G26"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G26:G27"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D21:E22"/>
-    <mergeCell ref="D24:E24"/>
     <mergeCell ref="D11:E12"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="C15:C16"/>
-    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="A11:A12"/>
